--- a/data/trans_camb/IP18A01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 10,61</t>
+          <t>-5,36; 10,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 4,43</t>
+          <t>-10,92; 4,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 7,73</t>
+          <t>-13,95; 5,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 6,37</t>
+          <t>-8,29; 6,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 6,5</t>
+          <t>-8,0; 6,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 10,56</t>
+          <t>-11,74; 12,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 6,01</t>
+          <t>-4,73; 6,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 2,97</t>
+          <t>-7,22; 2,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 4,88</t>
+          <t>-10,93; 3,92</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 135,9</t>
+          <t>-38,29; 132,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 60,46</t>
+          <t>-69,84; 65,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 132,97</t>
+          <t>-100,0; 100,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,92; 113,76</t>
+          <t>-64,81; 113,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,76; 113,59</t>
+          <t>-58,14; 102,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 184,74</t>
+          <t>-100,0; 206,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 70,73</t>
+          <t>-36,59; 84,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,23; 38,83</t>
+          <t>-54,76; 38,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,88; 66,96</t>
+          <t>-88,62; 58,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 6,12</t>
+          <t>-7,25; 6,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 10,52</t>
+          <t>-4,24; 9,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -4,47</t>
+          <t>-14,01; -4,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 10,23</t>
+          <t>-6,15; 10,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 7,35</t>
+          <t>-6,83; 7,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -4,61</t>
+          <t>-15,86; -4,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 6,56</t>
+          <t>-4,04; 6,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 6,67</t>
+          <t>-3,64; 6,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -5,64</t>
+          <t>-12,46; -5,4</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,86; 121,32</t>
+          <t>-64,0; 123,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 220,96</t>
+          <t>-38,14; 189,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 198,99</t>
+          <t>-44,67; 174,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,85; 152,17</t>
+          <t>-54,61; 173,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,51; 109,02</t>
+          <t>-36,52; 113,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 117,77</t>
+          <t>-31,88; 102,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 10,91</t>
+          <t>-3,91; 11,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 11,73</t>
+          <t>-5,07; 11,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 68,14</t>
+          <t>-8,64; 64,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 8,66</t>
+          <t>-4,77; 8,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 15,9</t>
+          <t>-0,01; 16,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 8,63</t>
+          <t>-8,57; 8,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,73</t>
+          <t>-2,27; 7,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 12,22</t>
+          <t>-0,36; 11,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 20,41</t>
+          <t>-6,42; 20,56</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 304,59</t>
+          <t>-39,07; 414,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 306,11</t>
+          <t>-51,76; 346,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2441,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 251,53</t>
+          <t>-53,38; 264,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 499,1</t>
+          <t>-12,99; 550,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 372,79</t>
+          <t>-100,0; 275,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 194,78</t>
+          <t>-28,59; 179,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 314,88</t>
+          <t>-10,61; 264,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 458,81</t>
+          <t>-100,0; 409,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 5,92</t>
+          <t>-4,72; 5,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 4,01</t>
+          <t>-5,74; 3,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 13,96</t>
+          <t>-6,79; 13,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 5,54</t>
+          <t>-4,19; 5,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 5,83</t>
+          <t>-4,15; 6,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 0,12</t>
+          <t>-10,34; 1,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,29</t>
+          <t>-2,54; 4,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,66</t>
+          <t>-3,42; 3,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 3,12</t>
+          <t>-7,17; 3,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 87,86</t>
+          <t>-40,97; 85,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,15; 53,15</t>
+          <t>-47,74; 60,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,75; 165,39</t>
+          <t>-66,06; 169,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 82,71</t>
+          <t>-35,51; 79,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 82,64</t>
+          <t>-36,28; 86,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,18</t>
+          <t>-100,0; 30,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 58,02</t>
+          <t>-23,14; 58,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 50,04</t>
+          <t>-30,39; 49,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,3; 41,87</t>
+          <t>-71,8; 47,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 4,32</t>
+          <t>-8,3; 4,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 3,22</t>
+          <t>-8,81; 3,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 1,94</t>
+          <t>-12,68; 2,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 10,72</t>
+          <t>-1,05; 10,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,94</t>
+          <t>-7,73; 1,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 6,69</t>
+          <t>-6,66; 7,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 6,58</t>
+          <t>-2,18; 6,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 1,18</t>
+          <t>-6,27; 1,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 2,26</t>
+          <t>-7,63; 2,15</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,92; 78,62</t>
+          <t>-62,04; 91,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,13; 58,73</t>
+          <t>-63,8; 69,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 80,59</t>
+          <t>-100,0; 71,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 322,12</t>
+          <t>-18,92; 323,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-88,41; 54,24</t>
+          <t>-88,81; 63,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,97; 218,77</t>
+          <t>-88,4; 231,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 125,03</t>
+          <t>-23,79; 120,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 24,19</t>
+          <t>-64,02; 27,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,36; 50,48</t>
+          <t>-82,4; 53,13</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 14,61</t>
+          <t>-1,57; 13,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,26; 22,17</t>
+          <t>4,0; 22,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 37,8</t>
+          <t>-3,82; 37,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 8,01</t>
+          <t>-9,89; 6,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 6,29</t>
+          <t>-11,35; 6,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,21; -6,19</t>
+          <t>-17,91; -5,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 8,37</t>
+          <t>-3,18; 7,58</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 11,26</t>
+          <t>-0,89; 11,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 12,46</t>
+          <t>-8,32; 11,35</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 1148,03</t>
+          <t>-50,75; 1241,63</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19,32; 1333,29</t>
+          <t>42,17; 1733,73</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-62,42; 127,12</t>
+          <t>-63,0; 98,68</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-74,82; 103,32</t>
+          <t>-73,69; 92,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 175,19</t>
+          <t>-35,4; 151,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 211,63</t>
+          <t>-18,05; 208,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 226,92</t>
+          <t>-100,0; 323,88</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,62</t>
+          <t>-1,56; 4,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,79</t>
+          <t>-1,45; 3,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,9</t>
+          <t>-5,49; 3,98</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,35</t>
+          <t>-1,01; 4,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,86</t>
+          <t>-2,45; 2,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,61; -1,17</t>
+          <t>-7,63; -1,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,37</t>
+          <t>-0,57; 3,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,31</t>
+          <t>-1,28; 2,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,81; -0,38</t>
+          <t>-5,73; -0,65</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 49,96</t>
+          <t>-14,91; 53,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 51,65</t>
+          <t>-14,66; 53,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 49,08</t>
+          <t>-57,07; 58,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 60,51</t>
+          <t>-11,42; 62,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 38,96</t>
+          <t>-24,89; 35,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-81,56; -12,17</t>
+          <t>-80,94; -14,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 43,49</t>
+          <t>-6,01; 43,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 30,52</t>
+          <t>-13,27; 31,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-61,81; -3,63</t>
+          <t>-64,29; -7,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 10,48</t>
+          <t>-6,65; 10,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 4,4</t>
+          <t>-11,51; 4,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 5,22</t>
+          <t>-13,64; 7,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 6,32</t>
+          <t>-9,01; 6,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 6,34</t>
+          <t>-7,48; 6,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 12,15</t>
+          <t>-10,96; 12,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 6,2</t>
+          <t>-5,18; 5,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 2,98</t>
+          <t>-7,06; 2,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 3,92</t>
+          <t>-10,48; 4,43</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 132,64</t>
+          <t>-43,79; 137,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,84; 65,8</t>
+          <t>-71,03; 59,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,48</t>
+          <t>-100,0; 120,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 113,83</t>
+          <t>-65,62; 109,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 102,27</t>
+          <t>-56,23; 118,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 206,08</t>
+          <t>-100,0; 227,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 84,57</t>
+          <t>-39,99; 69,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 38,18</t>
+          <t>-52,52; 37,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,62; 58,63</t>
+          <t>-83,39; 58,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 6,67</t>
+          <t>-7,02; 6,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 9,86</t>
+          <t>-4,6; 10,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -4,19</t>
+          <t>-14,47; -4,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 10,16</t>
+          <t>-5,19; 9,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 7,31</t>
+          <t>-6,89; 7,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -4,65</t>
+          <t>-16,02; -4,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 6,85</t>
+          <t>-4,52; 6,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 6,22</t>
+          <t>-3,54; 6,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,46; -5,4</t>
+          <t>-13,11; -5,66</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 123,31</t>
+          <t>-60,46; 148,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,14; 189,63</t>
+          <t>-44,39; 212,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,67; 174,01</t>
+          <t>-43,26; 176,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 173,09</t>
+          <t>-53,72; 157,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 113,47</t>
+          <t>-38,25; 95,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 102,42</t>
+          <t>-31,05; 105,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 11,9</t>
+          <t>-4,3; 11,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 11,97</t>
+          <t>-3,8; 12,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 64,91</t>
+          <t>-9,5; 61,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 8,46</t>
+          <t>-5,25; 8,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 16,52</t>
+          <t>-0,6; 16,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 8,05</t>
+          <t>-8,03; 10,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 7,4</t>
+          <t>-2,05; 7,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 11,47</t>
+          <t>-0,08; 11,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 20,56</t>
+          <t>-6,34; 20,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 414,59</t>
+          <t>-46,0; 340,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,76; 346,83</t>
+          <t>-44,88; 444,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 2149,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 264,63</t>
+          <t>-58,1; 249,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 550,26</t>
+          <t>-14,19; 447,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 275,79</t>
+          <t>-100,0; 391,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 179,73</t>
+          <t>-27,66; 172,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 264,68</t>
+          <t>-4,3; 274,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 409,59</t>
+          <t>-100,0; 497,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 5,57</t>
+          <t>-3,55; 6,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 3,92</t>
+          <t>-5,02; 4,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 13,55</t>
+          <t>-7,08; 11,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 5,36</t>
+          <t>-3,4; 5,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 6,01</t>
+          <t>-3,8; 6,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 1,1</t>
+          <t>-10,52; 0,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,44</t>
+          <t>-2,28; 4,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,78</t>
+          <t>-2,96; 3,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 3,34</t>
+          <t>-7,24; 4,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,97; 85,71</t>
+          <t>-32,64; 96,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 60,14</t>
+          <t>-43,57; 60,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 169,31</t>
+          <t>-66,68; 151,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 79,9</t>
+          <t>-30,19; 88,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 86,72</t>
+          <t>-34,05; 97,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,99</t>
+          <t>-100,0; 15,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 58,96</t>
+          <t>-20,93; 64,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 49,55</t>
+          <t>-27,14; 49,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,8; 47,02</t>
+          <t>-69,36; 57,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 4,98</t>
+          <t>-8,16; 4,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 3,85</t>
+          <t>-8,86; 3,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 2,07</t>
+          <t>-12,17; 1,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 10,81</t>
+          <t>-1,02; 11,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 1,26</t>
+          <t>-7,39; 1,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 7,25</t>
+          <t>-6,19; 7,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 6,28</t>
+          <t>-2,47; 6,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 1,22</t>
+          <t>-6,18; 1,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,15</t>
+          <t>-7,6; 3,11</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-62,04; 91,85</t>
+          <t>-60,16; 71,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 69,45</t>
+          <t>-63,03; 71,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 71,03</t>
+          <t>-100,0; 105,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 323,56</t>
+          <t>-19,31; 353,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-88,81; 63,85</t>
+          <t>-86,37; 76,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,4; 231,62</t>
+          <t>-81,19; 338,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 120,7</t>
+          <t>-26,07; 107,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 27,11</t>
+          <t>-62,06; 32,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,4; 53,13</t>
+          <t>-81,28; 70,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 13,92</t>
+          <t>-1,08; 13,57</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,0; 22,57</t>
+          <t>3,8; 24,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 37,57</t>
+          <t>-3,5; 34,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 6,58</t>
+          <t>-9,56; 7,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 6,01</t>
+          <t>-11,36; 6,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,91; -5,97</t>
+          <t>-18,62; -6,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 7,58</t>
+          <t>-3,2; 7,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 11,26</t>
+          <t>-1,71; 11,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 11,35</t>
+          <t>-7,91; 11,66</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 1241,63</t>
+          <t>-40,32; 1216,9</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>42,17; 1733,73</t>
+          <t>28,31; 1938,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,0; 98,68</t>
+          <t>-60,5; 109,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 92,58</t>
+          <t>-75,86; 93,67</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 151,82</t>
+          <t>-33,64; 153,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 208,13</t>
+          <t>-21,8; 207,86</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 323,88</t>
+          <t>-100,0; 288,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 4,19</t>
+          <t>-1,33; 4,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,84</t>
+          <t>-1,52; 3,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,98</t>
+          <t>-5,18; 3,83</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,49</t>
+          <t>-1,02; 4,43</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,53</t>
+          <t>-2,36; 2,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,63; -1,41</t>
+          <t>-7,47; -1,38</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,38</t>
+          <t>-0,51; 3,31</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,39</t>
+          <t>-1,38; 2,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -0,65</t>
+          <t>-5,8; -0,0</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 53,8</t>
+          <t>-13,56; 54,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 53,6</t>
+          <t>-15,99; 53,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,07; 58,67</t>
+          <t>-56,11; 51,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 62,28</t>
+          <t>-9,71; 61,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 35,81</t>
+          <t>-24,11; 36,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,94; -14,1</t>
+          <t>-80,26; -15,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 43,3</t>
+          <t>-5,69; 43,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 31,95</t>
+          <t>-14,24; 29,8</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-64,29; -7,43</t>
+          <t>-63,39; 0,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,93</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,82</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,36</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-5,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,66</t>
+          <t>-3,91</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 10,37</t>
+          <t>-7,91; 6,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 4,39</t>
+          <t>-7,32; 6,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 7,46</t>
+          <t>-11,1; 14,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 6,49</t>
+          <t>-6,43; 10,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 6,66</t>
+          <t>-10,47; 4,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 12,36</t>
+          <t>-12,98; 11,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 5,99</t>
+          <t>-4,89; 6,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,84</t>
+          <t>-7,26; 2,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 4,43</t>
+          <t>-10,07; 6,45</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-9,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-4,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-23,25%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>16,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-32,32%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-53,9%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-9,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,14%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-28,44%</t>
+          <t>-46,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-43,39%</t>
+          <t>-36,46%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 137,0</t>
+          <t>-60,92; 113,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,03; 59,97</t>
+          <t>-57,76; 113,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,37</t>
+          <t>-100,0; 213,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,62; 109,73</t>
+          <t>-44,05; 135,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 118,97</t>
+          <t>-71,09; 60,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,0</t>
+          <t>-100,0; 200,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 69,79</t>
+          <t>-36,29; 70,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 37,43</t>
+          <t>-54,23; 38,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 58,38</t>
+          <t>-84,41; 87,7</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,88</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-9,15</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-8,31</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-9,15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 6,88</t>
+          <t>-5,98; 10,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 10,16</t>
+          <t>-7,6; 7,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -4,56</t>
+          <t>-15,48; -4,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 9,63</t>
+          <t>-7,64; 6,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 7,56</t>
+          <t>-4,38; 10,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,02; -4,82</t>
+          <t>-13,9; -4,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 6,25</t>
+          <t>-4,35; 6,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 6,4</t>
+          <t>-3,54; 6,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,11; -5,66</t>
+          <t>-12,72; -5,64</t>
         </is>
       </c>
     </row>
@@ -946,27 +946,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-3,57%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34,91%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,46; 148,22</t>
+          <t>-46,4; 198,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 212,53</t>
+          <t>-56,85; 152,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 176,31</t>
+          <t>-63,86; 121,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 157,16</t>
+          <t>-39,36; 220,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 95,97</t>
+          <t>-37,51; 109,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 105,51</t>
+          <t>-31,96; 117,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,49</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-3,74</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,49</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>16,08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>0,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 11,52</t>
+          <t>-5,09; 8,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 12,88</t>
+          <t>-0,13; 15,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 61,57</t>
+          <t>-9,16; 5,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 8,82</t>
+          <t>-4,23; 10,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 16,11</t>
+          <t>-5,25; 11,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 10,08</t>
+          <t>-9,17; 70,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 7,8</t>
+          <t>-2,2; 7,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 11,55</t>
+          <t>0,41; 12,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 20,92</t>
+          <t>-6,53; 21,37</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>119,52%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-59,76%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>56,06%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>50,42%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>222,06%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27,07%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>119,52%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-47,72%</t>
+          <t>231,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 340,44</t>
+          <t>-59,95; 251,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 444,27</t>
+          <t>-5,56; 499,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2149,08</t>
+          <t>-100,0; 284,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 249,94</t>
+          <t>-44,36; 304,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 447,03</t>
+          <t>-54,15; 306,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 391,04</t>
+          <t>-100,0; 2420,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 172,63</t>
+          <t>-26,99; 194,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 274,67</t>
+          <t>-0,78; 314,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 497,17</t>
+          <t>-100,0; 475,84</t>
         </is>
       </c>
     </row>
@@ -1272,39 +1272,39 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,99</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,99</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,42</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,29</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-5,68</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0,3</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,85</t>
+          <t>-2,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 6,18</t>
+          <t>-3,92; 5,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 4,33</t>
+          <t>-3,76; 5,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 11,55</t>
+          <t>-10,67; -0,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 5,82</t>
+          <t>-4,33; 5,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 6,31</t>
+          <t>-5,46; 4,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 0,09</t>
+          <t>-6,62; 14,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,88</t>
+          <t>-2,43; 4,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 3,82</t>
+          <t>-3,17; 3,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 4,18</t>
+          <t>-7,13; 3,33</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-65,1%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>10,7%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-4,5%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-61,77%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-30,86%</t>
+          <t>-30,7%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 96,93</t>
+          <t>-35,05; 82,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 60,43</t>
+          <t>-33,26; 82,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 151,63</t>
+          <t>-97,35; 7,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 88,08</t>
+          <t>-37,09; 87,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 97,14</t>
+          <t>-47,15; 53,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,23</t>
+          <t>-67,79; 179,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 64,92</t>
+          <t>-23,18; 58,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 49,15</t>
+          <t>-28,7; 50,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,36; 57,76</t>
+          <t>-69,53; 49,72</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,98</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,42</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,05</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-5,88</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,98</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-6,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-3,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 4,19</t>
+          <t>-1,34; 10,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 3,87</t>
+          <t>-7,73; 0,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 1,93</t>
+          <t>-7,18; 5,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 11,39</t>
+          <t>-7,9; 4,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 1,19</t>
+          <t>-8,97; 3,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 7,48</t>
+          <t>-12,98; 0,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 6,01</t>
+          <t>-2,28; 6,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,4</t>
+          <t>-6,65; 1,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 3,11</t>
+          <t>-8,3; 0,82</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-53,64%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-28,85%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-14,99%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-21,53%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-61,84%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>83,72%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-53,64%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-17,04%</t>
+          <t>-68,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-41,8%</t>
+          <t>-50,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,16; 71,12</t>
+          <t>-26,99; 322,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,03; 71,94</t>
+          <t>-88,41; 54,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,05</t>
+          <t>-93,88; 177,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 353,2</t>
+          <t>-61,92; 78,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-86,37; 76,37</t>
+          <t>-66,13; 58,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 338,35</t>
+          <t>-100,0; 60,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 107,38</t>
+          <t>-24,07; 125,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 32,54</t>
+          <t>-65,24; 24,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-81,28; 70,0</t>
+          <t>-85,68; 28,27</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,94</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-3,02</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-11,19</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>5,44</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>12,56</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>9,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-3,02</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-11,19</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-2,3</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 13,57</t>
+          <t>-9,43; 8,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,8; 24,42</t>
+          <t>-11,54; 6,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 34,07</t>
+          <t>-19,21; -6,19</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 7,42</t>
+          <t>-1,21; 14,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 6,25</t>
+          <t>4,26; 22,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,62; -6,06</t>
+          <t>-3,83; 32,65</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 7,81</t>
+          <t>-3,11; 8,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 11,3</t>
+          <t>-1,23; 11,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 11,66</t>
+          <t>-8,13; 10,7</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-8,37%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-26,96%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>141,84%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>327,47%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>234,62%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-8,37%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-26,96%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>181,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-23,31%</t>
+          <t>-30,87%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 1216,9</t>
+          <t>-62,42; 127,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28,31; 1938,02</t>
+          <t>-74,82; 103,32</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,5; 109,04</t>
+          <t>-38,08; 1148,03</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-75,86; 93,67</t>
+          <t>19,32; 1333,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 153,1</t>
+          <t>-33,1; 175,19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 207,86</t>
+          <t>-16,29; 211,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 288,49</t>
+          <t>-100,0; 205,79</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-5,15</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,23</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,99</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,89</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-3,52</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,01</t>
+          <t>-1,07; 4,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,79</t>
+          <t>-2,46; 2,86</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,83</t>
+          <t>-7,79; -1,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,43</t>
+          <t>-2,02; 3,62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,63</t>
+          <t>-1,81; 3,79</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -1,38</t>
+          <t>-5,64; 3,98</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,31</t>
+          <t>-0,23; 3,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,31</t>
+          <t>-1,52; 2,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,0</t>
+          <t>-5,81; -0,38</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>19,3%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-60,68%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>14,19%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>11,44%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-16,41%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-57,62%</t>
+          <t>-16,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-39,71%</t>
+          <t>-40,98%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 54,98</t>
+          <t>-11,34; 60,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 53,01</t>
+          <t>-25,23; 38,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,11; 51,19</t>
+          <t>-83,14; -15,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 61,49</t>
+          <t>-19,57; 49,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 36,91</t>
+          <t>-17,83; 51,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,26; -15,03</t>
+          <t>-58,51; 50,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 43,57</t>
+          <t>-2,84; 43,49</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 29,8</t>
+          <t>-15,65; 30,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 0,33</t>
+          <t>-63,62; -3,98</t>
         </is>
       </c>
     </row>
